--- a/sheets/대금율보/검수/꽃밭에서.xlsx
+++ b/sheets/대금율보/검수/꽃밭에서.xlsx
@@ -5394,7 +5394,6 @@
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 潕</t>
         </is>
       </c>
@@ -5467,8 +5466,7 @@
       </c>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K5" s="23" t="inlineStr">
@@ -5520,7 +5518,6 @@
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-‹
 淋㳞</t>
         </is>
       </c>
@@ -5804,7 +5801,6 @@
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 無</t>
         </is>
       </c>
@@ -5814,7 +5810,6 @@
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 潢</t>
         </is>
       </c>
@@ -5906,7 +5901,6 @@
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-‹
 汰淋</t>
         </is>
       </c>
@@ -5918,7 +5912,6 @@
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕
-‹
 湳淋</t>
         </is>
       </c>
@@ -5992,7 +5985,6 @@
       <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 林</t>
         </is>
       </c>
@@ -6068,8 +6060,7 @@
       </c>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="I18" s="24" t="inlineStr">
@@ -6208,7 +6199,6 @@
       <c r="J20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 潢</t>
         </is>
       </c>
@@ -6316,7 +6306,6 @@
       <c r="F22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-‹
 湳淋</t>
         </is>
       </c>
@@ -6350,7 +6339,6 @@
       <c r="L22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-‹
 湳淋</t>
         </is>
       </c>
@@ -6425,7 +6413,6 @@
       <c r="F24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-‹
 潢</t>
         </is>
       </c>
@@ -6437,7 +6424,6 @@
       <c r="H24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-‹
 淋</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/꽃밭에서.xlsx
+++ b/sheets/대금율보/검수/꽃밭에서.xlsx
@@ -5267,24 +5267,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="85.11" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="63.43" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="63.43" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="63.43" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="63.43" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="63.43" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="63.43" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="63.43" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -5669,7 +5669,7 @@
       <c r="L9" s="21"/>
       <c r="M9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="63.43" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="63.43" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="63.43" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="63.43" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="63.43" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="63.43" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="63.43" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -5998,7 +5998,7 @@
       <c r="L16" s="21"/>
       <c r="M16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="63.43" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -6031,7 +6031,7 @@
       <c r="L17" s="21"/>
       <c r="M17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="63.43" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="63.43" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="63.43" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="63.43" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="63.43" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="25" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="63.43" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="M23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="63.43" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -6442,7 +6442,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="63.43" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="23"/>
@@ -6493,7 +6493,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="63.43" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
@@ -6542,6 +6542,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="47"/>
 </worksheet>
 </file>